--- a/modelo/Omie_Contas_Pagar_v1_1_5.xlsx
+++ b/modelo/Omie_Contas_Pagar_v1_1_5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BrunoMascio\Downloads\Teste Boletos Extração\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BrunoMascio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FCA6D8A-4E48-4D94-8AEC-08B3DA1E7E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B63BC-83CD-43D1-B565-05B003F75EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="xbQRkC5vJ01E7tMyKc9M7QvdPvqNl8VsgbLN3lZWFwrvKVEqQKZq2z1pCYaz1eZLs9vGAggAMKeLMe3Cpb57sw==" workbookSaltValue="8x3xQFE05BbvbxRq76D/5w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -1416,9 +1416,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>970280</xdr:colOff>
+      <xdr:colOff>974090</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>287337</xdr:rowOff>
+      <xdr:rowOff>283527</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
